--- a/sample_sov.xlsx
+++ b/sample_sov.xlsx
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -64,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -912,19 +915,19 @@
       <c r="L4" t="n">
         <v>500000</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="3" t="n">
         <v>48000000</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>13000000</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>8500000</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="3" t="n">
         <v>70000000</v>
       </c>
       <c r="R4" t="inlineStr">
@@ -942,10 +945,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="U4" s="3" t="n">
         <v>70000000</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4" s="3" t="n">
         <v>50000</v>
       </c>
       <c r="W4" t="n">
@@ -1005,43 +1008,55 @@
       <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>250,000</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>$20,000,000</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>$5,500,000</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>$3,200,000</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>$28,700,000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>28700000</v>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>28700000</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="V5" s="3" t="n">
         <v>25000</v>
       </c>
       <c r="W5" t="n">
@@ -1104,19 +1119,19 @@
       <c r="L6" t="n">
         <v>120000</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="3" t="n">
         <v>35000000</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3" t="n">
         <v>12000000</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="3" t="n">
         <v>67000000</v>
       </c>
       <c r="R6" t="inlineStr">
@@ -1134,10 +1149,10 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="U6" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6" s="3" t="n">
         <v>100000</v>
       </c>
       <c r="W6" t="n">
@@ -1191,28 +1206,36 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>1995</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>circa 1995</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
       </c>
       <c r="L7" t="n">
         <v>8000</v>
       </c>
-      <c r="M7" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>800000</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>400000</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>2400000</v>
       </c>
       <c r="R7" t="inlineStr">
@@ -1230,17 +1253,17 @@
           <t>No</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="U7" s="3" t="n">
         <v>2400000</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="W7" t="n">
         <v>32.7767</v>
       </c>
       <c r="X7" t="n">
-        <v>-96.797</v>
+        <v>999</v>
       </c>
     </row>
     <row r="8">
@@ -1296,19 +1319,21 @@
       <c r="L8" t="n">
         <v>60000</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="3" t="n">
         <v>55000000</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>40000000</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="P8" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>(5000)</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>125000000</v>
       </c>
       <c r="R8" t="inlineStr">
@@ -1323,13 +1348,13 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8" s="3" t="n">
         <v>250000</v>
       </c>
       <c r="W8" t="n">
@@ -1392,19 +1417,19 @@
       <c r="L9" t="n">
         <v>180000</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="3" t="n">
         <v>22000000</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>15000000</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="3" t="n">
         <v>46000000</v>
       </c>
       <c r="R9" t="inlineStr">
@@ -1419,13 +1444,13 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="n">
         <v>46000000</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9" s="3" t="n">
         <v>75000</v>
       </c>
       <c r="W9" t="n">
@@ -1488,19 +1513,19 @@
       <c r="L10" t="n">
         <v>45000</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="O10" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n">
         <v>14000000</v>
       </c>
       <c r="R10" t="inlineStr">
@@ -1515,13 +1540,13 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
+          <t>n</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10" s="3" t="n">
         <v>25000</v>
       </c>
       <c r="W10" t="n">
@@ -1584,19 +1609,19 @@
       <c r="L11" t="n">
         <v>95000</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="3" t="n">
         <v>16000000</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="3" t="n">
         <v>30500000</v>
       </c>
       <c r="R11" t="inlineStr">
@@ -1614,10 +1639,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="U11" s="3" t="n">
         <v>30500000</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11" s="3" t="n">
         <v>50000</v>
       </c>
       <c r="W11" t="n">

--- a/sample_sov.xlsx
+++ b/sample_sov.xlsx
@@ -11,6 +11,8 @@
     <sheet name="SOV 2024" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SOV 2025" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cleaned Data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Source References" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1653,22 +1655,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>206200000</v>
       </c>
@@ -1684,13 +1675,6 @@
       <c r="Q13" t="n">
         <v>383600000</v>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1791,4 +1775,2022 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>location_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>occupancy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>year_built</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>num_stories</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>square_footage</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>building_value</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>contents_value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>bi_value</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>other_value</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>tiv</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>flood_zone</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>earthquake_zone</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sprinklered</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>policy_limit</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>deductible</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HQ Office Tower</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>100 Main St</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="K2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>40.7128</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-74.006</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Distribution Center</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>500 Industrial Blvd</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>60601</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pre-Eng Metal</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>28700000</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>28700000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>41.8781</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-87.6298</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R&amp;D Campus Bldg A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1200 Innovation Dr</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>95110</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>37.3382</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-121.8863</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Retail Storefront</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>88 Commerce Ave</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>75201</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Masonry</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>800000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>32.7767</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Data Center</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2000 Server Rd</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ashburn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20147</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Data Center</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Steel Frame</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>125000000</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>39.0438</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-77.48739999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Manufacturing Plant</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>750 Factory Ln</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>48201</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pre-Eng Metal</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>180000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>75000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>42.3314</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-83.0458</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Regional Office</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>300 Park Ave</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>30301</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Masonry</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2012</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="W8" t="n">
+        <v>33.749</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-84.38800000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cold Storage Facility</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1500 Frost Way</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>55401</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Cold Storage</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Insulated Metal Panel</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2015</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>95000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>30500000</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>30500000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="W9" t="n">
+        <v>44.9778</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-93.265</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>location_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>location_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>occupancy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>year_built</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>num_stories</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>square_footage</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>building_value</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>contents_value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>bi_value</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>other_value</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>tiv</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>flood_zone</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>earthquake_zone</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sprinklered</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>policy_limit</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>deductible</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M4</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N4</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O4</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P4</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q4</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S4</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V4</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W4</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E5</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P5</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R5</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V5</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W5</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E6</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H6</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K6</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L6</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M6</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N6</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O6</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P6</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S6</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V6</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W6</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A7</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B7</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E7</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L7</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M7</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N7</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O7</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P7</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R7</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S7</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V7</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W7</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G8</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K8</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L8</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M8</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N8</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O8</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P8</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R8</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S8</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U8</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V8</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W8</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E9</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G9</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K9</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L9</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M9</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N9</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O9</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P9</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q9</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R9</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S9</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T9</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U9</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V9</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W9</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H10</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K10</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q10</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S10</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T10</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U10</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V10</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W10</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!A11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!B11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!C11</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!D11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!E11</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!F11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!G11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!H11</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!I11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!J11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!K11</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!L11</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!M11</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!N11</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!O11</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!P11</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!Q11</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!R11</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!S11</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!T11</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!U11</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!V11</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!W11</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>'SOV 2025'!X11</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>